--- a/per-stock/CRWD/financials.xlsx
+++ b/per-stock/CRWD/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>168874803200</v>
+        <v>174341259264</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>163896967168</v>
+        <v>170651254784</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -578,7 +587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>107.72588</v>
+        <v>109.58058</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -593,7 +602,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35.09448</v>
+        <v>34.223484</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -608,7 +617,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.74808997</v>
+        <v>0.75136</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -623,7 +632,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0100300005</v>
+        <v>-0.022079999</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -638,7 +647,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.033770002</v>
+        <v>-0.00598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -653,7 +662,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04137</v>
+        <v>-0.0024899999</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -668,7 +677,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.233</v>
+        <v>0.256</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -683,7 +692,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5230125056</v>
+        <v>4552800768</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -698,7 +707,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>820076992</v>
+        <v>821342976</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -713,11 +722,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1604615040</v>
+        <v>1431313000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -728,7 +737,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>254536521</v>
+        <v>254564820</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -743,7 +752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>663.46</v>
+        <v>684.86</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -787,6 +796,1330 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D43</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C43</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B43</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B43:E43)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D41</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C41</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B41</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B41:E41)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D34</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C34</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B34</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B34:E34)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D8</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C8</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B8</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B8:E8)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B4:E4)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D2/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C2/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2023-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tax Effect Of Unusual Items</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tax Rate For Calcs</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.305022</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Normalized EBITDA</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>182483000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>298831000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>276681000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>-40754000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Income From Continuing Operation Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>-162502000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>-15241000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>72181000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-183245000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Reconciled Depreciation</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>281451000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>213956000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>145254000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>93810000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Reconciled Cost Of Revenue</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1218929000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>990172000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>758929000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>601231000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>182483000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>298831000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>276681000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-40754000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-98968000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>84875000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>131427000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-134564000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Interest Income</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>166948000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>169863000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>123174000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>27176000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Interest Expense</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>28021000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>26311000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>25756000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>25319000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>194969000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>196174000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>148930000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>52495000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Normalized Income</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>-162502000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-15241000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>72181000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-183245000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net Income From Continuing And Discontinued Operation</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>-162502000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>-15241000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>72181000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-183245000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>5105297000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>4070024000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>3074696000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>2431348000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Total Operating Income As Reported</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-293292000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-116400000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-19141000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-190112000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Diluted Average Shares</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>250576000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>244750000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>243635000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>233139000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Basic Average Shares</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>250576000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>244750000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>238637000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>233139000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Diluted EPS</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Basic EPS</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Diluted NI Availto Com Stockholders</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-162502000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>-15241000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>72181000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-183245000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Net Income Common Stockholders</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>-162502000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>-15241000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>72181000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-183245000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>-162502000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-15241000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>72181000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-183245000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Minority Interests</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>-1337000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>-2675000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>-1258000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-960000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Net Income Including Noncontrolling Interests</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-161165000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-12566000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>73439000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-182285000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Net Income Continuous Operations</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>-161165000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>-12566000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>73439000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>-182285000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tax Provision</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>34176000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>71130000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>32232000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>22402000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Pretax Income</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>-126989000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>58564000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>105671000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>-159883000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Other Income Expense</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>-645000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>5101000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1638000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>3053000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Other Non Operating Income Expenses</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>-645000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>5101000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1638000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>3053000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Net Non Operating Interest Income Expense</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>166948000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>169863000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>123174000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>27176000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Interest Expense Non Operating</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>28021000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>26311000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>25756000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>25319000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Interest Income Non Operating</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>194969000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>196174000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>148930000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>52495000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>-293292000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>-116400000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>-19141000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>-190112000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Operating Expense</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>3886368000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>3079852000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>2315767000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>1830117000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Research And Development</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>1384770000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>1075587000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>780319000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>608364000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Selling General And Administration</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>2501598000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>2004265000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>1535448000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1221753000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Selling And Marketing Expense</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1831254000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>1523001000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>1140275000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>904409000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>General And Administrative Expense</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>670344000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>481264000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>395173000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>317344000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Other Gand A</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>670344000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>481264000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>395173000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>317344000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>3593076000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>2963452000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>2296626000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>1640005000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Cost Of Revenue</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>1218929000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>990172000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>758929000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>601231000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>4812005000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>3953624000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>3055555000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>2241236000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>4812005000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>3953624000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>3055555000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>2241236000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -811,27 +2144,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2022-01-31</t>
+          <t>2025-04-30</t>
         </is>
       </c>
     </row>
@@ -853,7 +2186,9 @@
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="3" t="n"/>
+      <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -865,15 +2200,17 @@
         <v>0.4</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>0.21</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.305022</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="F3" s="3" t="n"/>
+      <c r="F3" s="3" t="n">
+        <v>0.21</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -882,18 +2219,20 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>182483000</v>
+        <v>133106000</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>298831000</v>
+        <v>142899000</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>276681000</v>
+        <v>55512000</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-40754000</v>
-      </c>
-      <c r="F4" s="3" t="n"/>
+        <v>3187000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>-13172000</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -902,18 +2241,20 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-162502000</v>
+        <v>27774000</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>-15241000</v>
+        <v>59377000</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>72181000</v>
+        <v>-33997000</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-183245000</v>
-      </c>
-      <c r="F5" s="3" t="n"/>
+        <v>-77675000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>-104264000</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -922,18 +2263,20 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>281451000</v>
+        <v>87927000</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>213956000</v>
+        <v>77507000</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>145254000</v>
+        <v>71849000</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>93810000</v>
-      </c>
-      <c r="F6" s="3" t="n"/>
+        <v>68038000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>64057000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -942,18 +2285,20 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1218929000</v>
+        <v>342277000</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>990172000</v>
+        <v>311698000</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>758929000</v>
+        <v>307805000</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>601231000</v>
-      </c>
-      <c r="F7" s="3" t="n"/>
+        <v>310283000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>287875000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -962,18 +2307,20 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>182483000</v>
+        <v>133106000</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>298831000</v>
+        <v>142899000</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>276681000</v>
+        <v>55512000</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-40754000</v>
-      </c>
-      <c r="F8" s="3" t="n"/>
+        <v>3187000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>-13172000</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -982,18 +2329,20 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>-98968000</v>
+        <v>45179000</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>84875000</v>
+        <v>65392000</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>131427000</v>
+        <v>-16337000</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-134564000</v>
-      </c>
-      <c r="F9" s="3" t="n"/>
+        <v>-64851000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-77229000</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1002,18 +2351,20 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>166948000</v>
+        <v>34426000</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>169863000</v>
+        <v>40304000</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>123174000</v>
+        <v>43952000</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>27176000</v>
-      </c>
-      <c r="F10" s="3" t="n"/>
+        <v>44027000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>38665000</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1022,18 +2373,20 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>28021000</v>
+        <v>6116000</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>26311000</v>
+        <v>7552000</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>25756000</v>
+        <v>6931000</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>25319000</v>
-      </c>
-      <c r="F11" s="3" t="n"/>
+        <v>6823000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>6715000</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1042,18 +2395,20 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>194969000</v>
+        <v>40542000</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>196174000</v>
+        <v>47856000</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>148930000</v>
+        <v>50883000</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>52495000</v>
-      </c>
-      <c r="F12" s="3" t="n"/>
+        <v>50850000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>45380000</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1062,18 +2417,20 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-162502000</v>
+        <v>27774000</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-15241000</v>
+        <v>59377000</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>72181000</v>
+        <v>-33997000</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-183245000</v>
-      </c>
-      <c r="F13" s="3" t="n"/>
+        <v>-77675000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-104264000</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1082,18 +2439,20 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>-162502000</v>
+        <v>27774000</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>-15241000</v>
+        <v>59377000</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>72181000</v>
+        <v>-33997000</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-183245000</v>
-      </c>
-      <c r="F14" s="3" t="n"/>
+        <v>-77675000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-104264000</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1102,18 +2461,20 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5105297000</v>
+        <v>1416229000</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>4070024000</v>
+        <v>1291589000</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>3074696000</v>
+        <v>1303687000</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2431348000</v>
-      </c>
-      <c r="F15" s="3" t="n"/>
+        <v>1281931000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1222147000</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1122,18 +2483,20 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-293292000</v>
+        <v>-30600000</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-116400000</v>
+        <v>13786000</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-19141000</v>
+        <v>-69443000</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-190112000</v>
-      </c>
-      <c r="F16" s="3" t="n"/>
+        <v>-112979000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-118713000</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1141,18 +2504,20 @@
           <t>Diluted Average Shares</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
+      <c r="B17" s="3" t="n">
+        <v>257881000</v>
+      </c>
       <c r="C17" s="3" t="n">
-        <v>244750000</v>
+        <v>258133000</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>243635000</v>
+        <v>251326000</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>233139000</v>
+        <v>249909000</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>227142000</v>
+        <v>248432000</v>
       </c>
     </row>
     <row r="18">
@@ -1161,18 +2526,20 @@
           <t>Basic Average Shares</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
+      <c r="B18" s="3" t="n">
+        <v>253732000</v>
+      </c>
       <c r="C18" s="3" t="n">
-        <v>244750000</v>
+        <v>252566000</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>238637000</v>
+        <v>251326000</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>233139000</v>
+        <v>249909000</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>227142000</v>
+        <v>248432000</v>
       </c>
     </row>
     <row r="19">
@@ -1181,18 +2548,20 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
+      <c r="B19" s="3" t="n">
+        <v>0.11</v>
+      </c>
       <c r="C19" s="3" t="n">
-        <v>-0.08</v>
+        <v>0.15</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.37</v>
+        <v>-0.14</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.31</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-1.03</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="20">
@@ -1201,18 +2570,20 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
+      <c r="B20" s="3" t="n">
+        <v>0.11</v>
+      </c>
       <c r="C20" s="3" t="n">
-        <v>-0.08</v>
+        <v>0.15</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.37</v>
+        <v>-0.14</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.31</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-1.03</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="21">
@@ -1222,18 +2593,20 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-162502000</v>
+        <v>27774000</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-15241000</v>
+        <v>59377000</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>72181000</v>
+        <v>-33997000</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-183245000</v>
-      </c>
-      <c r="F21" s="3" t="n"/>
+        <v>-77675000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>-104264000</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1242,18 +2615,20 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-162502000</v>
+        <v>27774000</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>-15241000</v>
+        <v>59377000</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>72181000</v>
+        <v>-33997000</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>-183245000</v>
-      </c>
-      <c r="F22" s="3" t="n"/>
+        <v>-77675000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>-104264000</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1262,18 +2637,20 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-162502000</v>
+        <v>27774000</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-15241000</v>
+        <v>59377000</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>72181000</v>
+        <v>-33997000</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-183245000</v>
-      </c>
-      <c r="F23" s="3" t="n"/>
+        <v>-77675000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-104264000</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1282,18 +2659,20 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-1337000</v>
+        <v>-18192000</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>-2675000</v>
+        <v>-2084000</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-1258000</v>
+        <v>-9000</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-960000</v>
-      </c>
-      <c r="F24" s="3" t="n"/>
+        <v>-30000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>786000</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1302,18 +2681,20 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-161165000</v>
+        <v>45966000</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>-12566000</v>
+        <v>61461000</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>73439000</v>
+        <v>-33988000</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-182285000</v>
-      </c>
-      <c r="F25" s="3" t="n"/>
+        <v>-77645000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-105050000</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1322,18 +2703,20 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-161165000</v>
+        <v>45966000</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-12566000</v>
+        <v>61461000</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>73439000</v>
+        <v>-33988000</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-182285000</v>
-      </c>
-      <c r="F26" s="3" t="n"/>
+        <v>-77645000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>-105050000</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1342,18 +2725,20 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>34176000</v>
+        <v>-6903000</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>71130000</v>
+        <v>-3621000</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>32232000</v>
+        <v>10720000</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>22402000</v>
-      </c>
-      <c r="F27" s="3" t="n"/>
+        <v>5971000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>21106000</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1362,18 +2747,20 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-126989000</v>
+        <v>39063000</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>58564000</v>
+        <v>57840000</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>105671000</v>
+        <v>-23268000</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-159883000</v>
-      </c>
-      <c r="F28" s="3" t="n"/>
+        <v>-71674000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>-83944000</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1382,18 +2769,20 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-645000</v>
+        <v>35237000</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>5101000</v>
+        <v>3750000</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1638000</v>
+        <v>2223000</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3053000</v>
-      </c>
-      <c r="F29" s="3" t="n"/>
+        <v>-2722000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-3896000</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1402,18 +2791,20 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-645000</v>
+        <v>35237000</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5101000</v>
+        <v>3750000</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1638000</v>
+        <v>2223000</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>3053000</v>
-      </c>
-      <c r="F30" s="3" t="n"/>
+        <v>-2722000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>-3896000</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1422,18 +2813,20 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>166948000</v>
+        <v>34426000</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>169863000</v>
+        <v>40304000</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>123174000</v>
+        <v>43952000</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>27176000</v>
-      </c>
-      <c r="F31" s="3" t="n"/>
+        <v>44027000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>38665000</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1442,18 +2835,20 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>28021000</v>
+        <v>6116000</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>26311000</v>
+        <v>7552000</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>25756000</v>
+        <v>6931000</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>25319000</v>
-      </c>
-      <c r="F32" s="3" t="n"/>
+        <v>6823000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>6715000</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1462,18 +2857,20 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>194969000</v>
+        <v>40542000</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>196174000</v>
+        <v>47856000</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>148930000</v>
+        <v>50883000</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>52495000</v>
-      </c>
-      <c r="F33" s="3" t="n"/>
+        <v>50850000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>45380000</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1482,18 +2879,20 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>-293292000</v>
+        <v>-30600000</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>-116400000</v>
+        <v>13786000</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>-19141000</v>
+        <v>-69443000</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>-190112000</v>
-      </c>
-      <c r="F34" s="3" t="n"/>
+        <v>-112979000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>-118713000</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1502,18 +2901,20 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>3886368000</v>
+        <v>1073952000</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>3079852000</v>
+        <v>979891000</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>2315767000</v>
+        <v>995882000</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1830117000</v>
-      </c>
-      <c r="F35" s="3" t="n"/>
+        <v>971648000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>934272000</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1522,18 +2923,20 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1384770000</v>
+        <v>408326000</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1075587000</v>
+        <v>356409000</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>780319000</v>
+        <v>347564000</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>608364000</v>
-      </c>
-      <c r="F36" s="3" t="n"/>
+        <v>346668000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>330926000</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1542,18 +2945,20 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>2501598000</v>
+        <v>665626000</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2004265000</v>
+        <v>623482000</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1535448000</v>
+        <v>648318000</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1221753000</v>
-      </c>
-      <c r="F37" s="3" t="n"/>
+        <v>624980000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>603346000</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1562,18 +2967,20 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>1831254000</v>
+        <v>488674000</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1523001000</v>
+        <v>463581000</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1140275000</v>
+        <v>481032000</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>904409000</v>
-      </c>
-      <c r="F38" s="3" t="n"/>
+        <v>447024000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>439211000</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1582,18 +2989,20 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>670344000</v>
+        <v>176952000</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>481264000</v>
+        <v>159901000</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>395173000</v>
+        <v>167286000</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>317344000</v>
-      </c>
-      <c r="F39" s="3" t="n"/>
+        <v>177956000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>164135000</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1602,18 +3011,20 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>670344000</v>
+        <v>176952000</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>481264000</v>
+        <v>159901000</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>395173000</v>
+        <v>167286000</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>317344000</v>
-      </c>
-      <c r="F40" s="3" t="n"/>
+        <v>177956000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>164135000</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1622,18 +3033,20 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>3593076000</v>
+        <v>1043352000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>2963452000</v>
+        <v>993677000</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>2296626000</v>
+        <v>926439000</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1640005000</v>
-      </c>
-      <c r="F41" s="3" t="n"/>
+        <v>858669000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>815559000</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1642,18 +3055,20 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>1218929000</v>
+        <v>342277000</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>990172000</v>
+        <v>311698000</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>758929000</v>
+        <v>307805000</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>601231000</v>
-      </c>
-      <c r="F42" s="3" t="n"/>
+        <v>310283000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>287875000</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1662,18 +3077,20 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>4812005000</v>
+        <v>1385629000</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>3953624000</v>
+        <v>1305375000</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>3055555000</v>
+        <v>1234244000</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>2241236000</v>
-      </c>
-      <c r="F43" s="3" t="n"/>
+        <v>1168952000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1103434000</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1682,1025 +3099,27 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>4812005000</v>
+        <v>1385629000</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>3953624000</v>
+        <v>1305375000</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>3055555000</v>
+        <v>1234244000</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>2241236000</v>
-      </c>
-      <c r="F44" s="3" t="n"/>
+        <v>1168952000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>1103434000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>2025-04-30</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Tax Effect Of Unusual Items</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tax Rate For Calcs</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Normalized EBITDA</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>142899000</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>55512000</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>3187000</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>-19115000</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>17641000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Net Income From Continuing Operation Net Minority Interest</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>59377000</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>-33997000</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>-77675000</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>-110207000</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>-92282000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Reconciled Depreciation</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>77507000</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>71849000</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>68038000</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>64057000</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>57440000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Reconciled Cost Of Revenue</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>311698000</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>307805000</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>310283000</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>289143000</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>273990000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>142899000</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>55512000</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>3187000</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>-19115000</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>17641000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>65392000</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>-16337000</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>-64851000</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>-83172000</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-39799000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Net Interest Income</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>40304000</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>43952000</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>44027000</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>38665000</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>39933000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Interest Expense</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>7552000</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>6931000</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>6823000</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>6715000</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>6664000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Interest Income</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>47856000</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>50883000</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>50850000</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>45380000</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>46597000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Normalized Income</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>59377000</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>-33997000</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>-77675000</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-110207000</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>-92282000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Net Income From Continuing And Discontinued Operation</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>59377000</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>-33997000</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>-77675000</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>-110207000</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>-92282000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Total Expenses</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>1291589000</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>1303687000</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>1281931000</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>1228090000</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>1143839000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Total Operating Income As Reported</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>13786000</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>-69443000</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>-112979000</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>-124656000</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>-85301000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Diluted Average Shares</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>258133000</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>251326000</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>249909000</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>248432000</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>246933000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Basic Average Shares</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>252566000</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>251326000</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>249909000</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>248432000</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>246933000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Diluted EPS</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Basic EPS</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Diluted NI Availto Com Stockholders</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>59377000</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>-33997000</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>-77675000</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-110207000</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>-92282000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Net Income Common Stockholders</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>59377000</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>-33997000</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>-77675000</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>-110207000</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>-92282000</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Net Income</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>59377000</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>-33997000</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>-77675000</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>-110207000</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>-92282000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Minority Interests</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>-2084000</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>-9000</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>-30000</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>786000</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>449000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Net Income Including Noncontrolling Interests</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>61461000</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>-33988000</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>-77645000</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>-110993000</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>-92731000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Net Income Continuous Operations</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>61461000</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>-33988000</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>-77645000</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>-110993000</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>-92731000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Tax Provision</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>-3621000</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>10720000</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>5971000</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>21106000</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>46268000</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Pretax Income</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>57840000</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>-23268000</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>-71674000</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>-89887000</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>-46463000</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Other Income Expense</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>2223000</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>-2722000</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>-3896000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>-1095000</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Other Non Operating Income Expenses</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>2223000</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>-2722000</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>-3896000</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>-1095000</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Net Non Operating Interest Income Expense</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>40304000</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>43952000</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>44027000</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>38665000</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>39933000</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Interest Expense Non Operating</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>7552000</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>6931000</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>6823000</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>6715000</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>6664000</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Interest Income Non Operating</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>47856000</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>50883000</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>50850000</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>45380000</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>46597000</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Operating Income</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>13786000</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>-69443000</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>-112979000</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>-124656000</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>-85301000</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Operating Expense</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>979891000</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>995882000</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>971648000</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>938947000</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>869849000</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Research And Development</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>356409000</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>347564000</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>346668000</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>334129000</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>315142000</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Selling General And Administration</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>623482000</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>648318000</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>624980000</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>604818000</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>554707000</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Selling And Marketing Expense</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>463581000</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>481032000</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>447024000</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>439617000</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>409504000</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>General And Administrative Expense</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>159901000</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>167286000</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>177956000</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>165201000</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>145203000</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Other Gand A</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>159901000</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>167286000</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>177956000</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>165201000</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>145203000</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>993677000</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>926439000</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>858669000</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>814291000</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>784548000</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Cost Of Revenue</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>311698000</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>307805000</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>310283000</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>289143000</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>273990000</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>1305375000</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>1234244000</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>1168952000</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>1103434000</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>1058538000</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Operating Revenue</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>1305375000</v>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>1234244000</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>1168952000</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>1103434000</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>1058538000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4210,7 +4629,1737 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>254536521</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>253363000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>252078000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>250827000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>249074000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>254536521</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>253363000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>252078000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>250827000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>249074000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>821343000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>820077000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>818046000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>810528000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>785398000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2080645000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2928394000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>2519165000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2725497000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>2412106000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>5379720000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>5173861000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>4761596000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4501407000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>4195232000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2185758000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3234927000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2919387000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>3058416000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>2788264000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>2080645000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>2928394000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2519165000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2725497000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>2412106000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>75500000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>74606000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>72947000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>65801000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>41043000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>4633877000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>4428390000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>4016497000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>3756680000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>3450877000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>5379720000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>5173861000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>4761596000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>4501407000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>4195232000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>4675332000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>4472605000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>4059017000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>3794691000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>3491014000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>41455000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>44215000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>42520000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>38011000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>40137000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>4633877000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>4428390000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>4016497000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>3756680000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>3450877000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>35649000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>16756000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1537000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>5855000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>35649000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>16756000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1537000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>5855000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-1255268000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-1283042000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-1299986000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-1265989000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-1188314000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>5853369000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>5694549000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>5314820000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>5016544000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>4633211000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>127000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>127000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>126000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>125000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>125000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>127000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>127000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>126000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>125000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>125000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>6594768000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>6614079000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>5906330000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>5494168000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>5229348000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>2478906000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>2429887000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>2306435000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>2018230000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>1946814000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>325497000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>295655000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>292556000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>166901000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>149122000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>1351960000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>1332387000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1211762000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>1053661000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>1024258000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1351960000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>1332387000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1211762000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1053661000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1024258000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>801449000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>801845000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>802117000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>797668000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>773434000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>55606000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>56374000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>57018000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>52941000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>29079000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>745843000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>745471000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>745099000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>744727000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>744355000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>4115862000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>4184192000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>3599895000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>3475938000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>3282534000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>103243000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>68811000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>53220000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>51278000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>53652000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>3370233000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>3421051000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>2851488000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>2781196000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>2747137000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>3370233000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>3421051000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>2851488000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>2781196000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>2747137000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>19894000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>18232000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>15929000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>12860000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>11964000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>19894000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>18232000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>15929000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>12860000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>11964000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>78534000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>36193000</v>
+      </c>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n">
+        <v>70698000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>70698000</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>33214000</v>
+      </c>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>543958000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>639905000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>679258000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>559906000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>399083000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>489737000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>534586000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>547662000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>439352000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>382679000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n">
+        <v>4750000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>54221000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>105319000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>131596000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>120554000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>16404000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>54221000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>105319000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>131596000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>120554000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>16404000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>11270100000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>11086684000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>9965347000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>9288859000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>8720362000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>4968480000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>3667565000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>3446065000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>2754505000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>2649564000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>469488000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>388888000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>316858000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>201113000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>178150000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>743200000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>655658000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>556221000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>517088000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>496045000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>66263000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>76832000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>81332000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>72482000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>71339000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Other Investments</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>66263000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>76832000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>81332000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>72482000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>71339000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>2553232000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>1499996000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>1497332000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>1031183000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>1038771000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>285739000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>136702000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>144405000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>117858000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>125486000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>2267493000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>1363294000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1352927000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>913325000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>913285000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>1136297000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>1046191000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>994322000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>932639000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>865259000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>-842673000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>-770672000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>-702841000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>-641515000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>-581814000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>1978970000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>1816863000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>1697163000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>1574154000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1447073000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>63205000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>54305000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>50151000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>44510000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>42998000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>282393000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>219509000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>227502000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>214608000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>215871000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>70093000</v>
+      </c>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n">
+        <v>46289000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>1563279000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>1473189000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1352151000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>1251637000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1149014000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>70093000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>69860000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>67359000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>63399000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>39190000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>6301620000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>7419119000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>6519282000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>6534354000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>6070798000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>186663000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>379695000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>306375000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>302818000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>296146000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>353869000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>447455000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>398708000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>372543000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>351805000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>274400000</v>
+      </c>
+      <c r="C63" s="3" t="n"/>
+      <c r="D63" s="3" t="n"/>
+      <c r="E63" s="3" t="n"/>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>933887000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>1361844000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>1013116000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>886557000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>808694000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>933887000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>1361844000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>1013116000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>886557000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>808694000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>-3100000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>-2700000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>-2700000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>936987000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1364844000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1015816000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>889557000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>811394000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>4552801000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>5230125000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>4801083000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>4972436000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>4614153000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n"/>
+      <c r="D69" s="3" t="n"/>
+      <c r="E69" s="3" t="n"/>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>4552801000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>5230125000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>4801083000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>4972436000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>4614153000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n">
+        <v>3100000000</v>
+      </c>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Cash Financial</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n">
+        <v>2130125000</v>
+      </c>
+      <c r="D72" s="3" t="n"/>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n">
+        <v>323295000</v>
+      </c>
+      <c r="H72" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5414,13 +7563,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5430,6 +7579,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5440,30 +7590,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -5476,1137 +7631,1245 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>470742000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>378149000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>297376000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>285046000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>280919000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>240808000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Capital Expenditure</t>
+          <t>Repurchase Of Capital Stock</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-119720000</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>-100165000</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>-47786000</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>-103188000</v>
-      </c>
+        <v>-175622000</v>
+      </c>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n">
-        <v>-104914000</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Interest Paid Supplemental Data</t>
+          <t>Capital Expenditure</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>-120195000</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>11250000</v>
+        <v>-119720000</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>-100165000</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>11250000</v>
+        <v>-47786000</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>-103188000</v>
       </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Income Tax Paid Supplemental Data</t>
+          <t>Interest Paid Supplemental Data</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>9959000</v>
+        <v>11250000</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>15474000</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>9005000</v>
+        <v>11250000</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>17026000</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>4827000</v>
+        <v>11250000</v>
       </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>End Cash Position</t>
+          <t>Income Tax Paid Supplemental Data</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>5314617000</v>
+        <v>23314000</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4886054000</v>
+        <v>9959000</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4973912000</v>
+        <v>15474000</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4615623000</v>
+        <v>9005000</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4324666000</v>
+        <v>17026000</v>
       </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Beginning Cash Position</t>
+          <t>End Cash Position</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>4715726000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>5314617000</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>4886054000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>4973912000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>4615623000</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>4324666000</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>4262214000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Effect Of Exchange Rate Changes</t>
+          <t>Beginning Cash Position</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>2312000</v>
+        <v>5314617000</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>722000</v>
+        <v>4886054000</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>49000</v>
+        <v>4973912000</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>6546000</v>
+        <v>4615623000</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-4637000</v>
+        <v>4324666000</v>
       </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Changes In Cash</t>
+          <t>Effect Of Exchange Rate Changes</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>426251000</v>
+        <v>116000</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-88580000</v>
+        <v>2312000</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>358240000</v>
+        <v>722000</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>284411000</v>
+        <v>49000</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>67089000</v>
+        <v>6546000</v>
       </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Financing Cash Flow</t>
+          <t>Changes In Cash</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>51358000</v>
+        <v>-599007000</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4773000</v>
+        <v>426251000</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>74187000</v>
+        <v>-88580000</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2134000</v>
+        <v>358240000</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46386000</v>
+        <v>284411000</v>
       </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Financing Activities</t>
+          <t>Financing Cash Flow</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-195891000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>51358000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>4773000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>74187000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>2134000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>46386000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Net Other Financing Charges</t>
+          <t>Cash Flow From Continuing Financing Activities</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-389000</v>
+        <v>-195891000</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>4500000</v>
+        <v>51358000</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-2156000</v>
+        <v>4773000</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1500000</v>
+        <v>74187000</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2194000</v>
+        <v>2134000</v>
       </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Proceeds From Stock Option Exercised</t>
+          <t>Net Other Financing Charges</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>51747000</v>
+        <v>-20952000</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>273000</v>
+        <v>-389000</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>76343000</v>
+        <v>4500000</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>634000</v>
+        <v>-2156000</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>44192000</v>
+        <v>1500000</v>
       </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Investing Cash Flow</t>
+          <t>Proceeds From Stock Option Exercised</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>-122976000</v>
+        <v>683000</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>-490894000</v>
+        <v>51747000</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>-48779000</v>
+        <v>273000</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-101830000</v>
+        <v>76343000</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-325019000</v>
+        <v>634000</v>
       </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Investing Activities</t>
+          <t>Net Common Stock Issuance</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-122976000</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>-490894000</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>-48779000</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>-101830000</v>
-      </c>
+        <v>-175622000</v>
+      </c>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n">
-        <v>-325019000</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Net Investment Purchase And Sale</t>
+          <t>Common Stock Payments</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-1902000</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>-9815000</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>-993000</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>1358000</v>
-      </c>
+        <v>-175622000</v>
+      </c>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n">
-        <v>-6229000</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sale Of Investment</t>
+          <t>Investing Cash Flow</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>350000</v>
+        <v>-994053000</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>522000</v>
+        <v>-122976000</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1361000</v>
+        <v>-490894000</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3191000</v>
+        <v>-48779000</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1677000</v>
+        <v>-101830000</v>
       </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Purchase Of Investment</t>
+          <t>Cash Flow From Continuing Investing Activities</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-2252000</v>
+        <v>-994053000</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-10337000</v>
+        <v>-122976000</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>-2354000</v>
+        <v>-490894000</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-1833000</v>
+        <v>-48779000</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-7906000</v>
+        <v>-101830000</v>
       </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Net Business Purchase And Sale</t>
+          <t>Net Investment Purchase And Sale</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-1354000</v>
+        <v>7518000</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>-380914000</v>
+        <v>-1902000</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0</v>
+        <v>-9815000</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0</v>
+        <v>-993000</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-213876000</v>
+        <v>1358000</v>
       </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Purchase Of Business</t>
+          <t>Sale Of Investment</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-1354000</v>
+        <v>10266000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-380914000</v>
+        <v>350000</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>522000</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0</v>
+        <v>1361000</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-213876000</v>
+        <v>3191000</v>
       </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Net Intangibles Purchase And Sale</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
+          <t>Purchase Of Investment</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-2748000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>-2252000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>-10337000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-2354000</v>
+      </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-1833000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Purchase Of Intangibles</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
+          <t>Net Business Purchase And Sale</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>-881376000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>-1354000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>-380914000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Net PPE Purchase And Sale</t>
+          <t>Purchase Of Business</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-102465000</v>
+        <v>-881376000</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-83395000</v>
+        <v>-1354000</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-30497000</v>
+        <v>-380914000</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-85751000</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-87211000</v>
+        <v>0</v>
       </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Purchase Of PPE</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>-102465000</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>-83395000</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>-30497000</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>-85751000</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>-87211000</v>
-      </c>
-      <c r="G24" s="3" t="n"/>
+          <t>Net Intangibles Purchase And Sale</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Capital Expenditure Reported</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>-17255000</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>-16770000</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>-17289000</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>-17437000</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>-17703000</v>
-      </c>
-      <c r="G25" s="3" t="n"/>
+          <t>Purchase Of Intangibles</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Operating Cash Flow</t>
+          <t>Net PPE Purchase And Sale</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>497869000</v>
+        <v>-97624000</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>397541000</v>
+        <v>-102465000</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>332832000</v>
+        <v>-83395000</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>384107000</v>
+        <v>-30497000</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>345722000</v>
+        <v>-85751000</v>
       </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Operating Activities</t>
+          <t>Purchase Of PPE</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>497869000</v>
+        <v>-97624000</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>397541000</v>
+        <v>-102465000</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>332832000</v>
+        <v>-83395000</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>384107000</v>
+        <v>-30497000</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>345722000</v>
+        <v>-85751000</v>
       </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Change In Working Capital</t>
+          <t>Capital Expenditure Reported</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-31916000</v>
+        <v>-22571000</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>-39890000</v>
+        <v>-17255000</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-56849000</v>
+        <v>-16770000</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>69364000</v>
+        <v>-17289000</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>19035000</v>
+        <v>-17437000</v>
       </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Change In Other Working Capital</t>
+          <t>Operating Cash Flow</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>418141000</v>
+        <v>590937000</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>47459000</v>
+        <v>497869000</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-85357000</v>
+        <v>397541000</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-60087000</v>
+        <v>332832000</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>304012000</v>
+        <v>384107000</v>
       </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Change In Other Current Liabilities</t>
+          <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-4713000</v>
+        <v>590937000</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-866000</v>
+        <v>497869000</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-3527000</v>
+        <v>397541000</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-4586000</v>
+        <v>332832000</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-3845000</v>
+        <v>384107000</v>
       </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Change In Payables And Accrued Expense</t>
+          <t>Change In Working Capital</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>30097000</v>
+        <v>102281000</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>68358000</v>
+        <v>-31916000</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>139314000</v>
+        <v>-39890000</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-164839000</v>
+        <v>-56849000</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>179671000</v>
+        <v>69364000</v>
       </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Change In Accrued Expense</t>
+          <t>Change In Other Working Capital</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>31737000</v>
+        <v>-129422000</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>64675000</v>
+        <v>418141000</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>69396000</v>
+        <v>47459000</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>-81611000</v>
+        <v>-85357000</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>128828000</v>
+        <v>-60087000</v>
       </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Change In Payable</t>
+          <t>Change In Other Current Liabilities</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>-1640000</v>
+        <v>-4161000</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>3683000</v>
+        <v>-4713000</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>69918000</v>
+        <v>-866000</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-83228000</v>
+        <v>-3527000</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>50843000</v>
+        <v>-4586000</v>
       </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Change In Account Payable</t>
+          <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>-1640000</v>
+        <v>-117978000</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>3683000</v>
+        <v>30097000</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>69918000</v>
+        <v>68358000</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>-83228000</v>
+        <v>139314000</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>50843000</v>
+        <v>-164839000</v>
       </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Change In Prepaid Assets</t>
+          <t>Change In Accrued Expense</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-126717000</v>
+        <v>-63624000</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-29029000</v>
+        <v>31737000</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-29416000</v>
+        <v>64675000</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-20995000</v>
+        <v>69396000</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-147400000</v>
+        <v>-81611000</v>
       </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Change In Receivables</t>
+          <t>Change In Payable</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-348724000</v>
+        <v>-54354000</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>-125812000</v>
+        <v>-1640000</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-77863000</v>
+        <v>3683000</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>319871000</v>
+        <v>69918000</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>-313403000</v>
+        <v>-83228000</v>
       </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Changes In Account Receivables</t>
+          <t>Change In Account Payable</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-348724000</v>
+        <v>-54354000</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-125812000</v>
+        <v>-1640000</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-77863000</v>
+        <v>3683000</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>319871000</v>
+        <v>69918000</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-313403000</v>
+        <v>-83228000</v>
       </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Other Non Cash Items</t>
+          <t>Change In Prepaid Assets</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>130462000</v>
+        <v>-74992000</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>120641000</v>
+        <v>-126717000</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>112774000</v>
+        <v>-29029000</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>108177000</v>
+        <v>-29416000</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>96322000</v>
+        <v>-20995000</v>
       </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Stock Based Compensation</t>
+          <t>Change In Receivables</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>273951000</v>
+        <v>428834000</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>281971000</v>
+        <v>-348724000</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>287153000</v>
+        <v>-125812000</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>253604000</v>
+        <v>-77863000</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>272531000</v>
+        <v>319871000</v>
       </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Unrealized Gain Loss On Investment Securities</t>
+          <t>Changes In Account Receivables</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>428834000</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>-348724000</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>-125812000</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1579000</v>
-      </c>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-77863000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>319871000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Amortization Of Securities</t>
+          <t>Other Non Cash Items</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0</v>
+        <v>104253000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>130462000</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0</v>
+        <v>120641000</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>112774000</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>108177000</v>
       </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Deferred Tax</t>
+          <t>Stock Based Compensation</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>-9435000</v>
+        <v>297703000</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>-3042000</v>
+        <v>273951000</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>-639000</v>
+        <v>281971000</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>-1681000</v>
+        <v>293096000</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>-7781000</v>
+        <v>247661000</v>
       </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Deferred Income Tax</t>
+          <t>Unrealized Gain Loss On Investment Securities</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>-9435000</v>
+        <v>0</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>-3042000</v>
+        <v>0</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>-639000</v>
+        <v>0</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>-1681000</v>
+        <v>0</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>-7781000</v>
+        <v>1579000</v>
       </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>77507000</v>
-      </c>
+          <t>Amortization Of Securities</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n"/>
       <c r="C44" s="3" t="n">
-        <v>71849000</v>
+        <v>0</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>68038000</v>
+        <v>0</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>64057000</v>
+        <v>0</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>57440000</v>
-      </c>
-      <c r="G44" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization</t>
+          <t>Deferred Tax</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>77507000</v>
+        <v>-10831000</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>71849000</v>
+        <v>-9435000</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>68038000</v>
+        <v>-3042000</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>64057000</v>
+        <v>-639000</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>57440000</v>
+        <v>-1681000</v>
       </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Amortization Cash Flow</t>
+          <t>Deferred Income Tax</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>8172000</v>
+        <v>-10831000</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>7800000</v>
+        <v>-9435000</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>7627000</v>
+        <v>-3042000</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>7634000</v>
+        <v>-639000</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>7339000</v>
+        <v>-1681000</v>
       </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Amortization Of Intangibles</t>
+          <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>8172000</v>
+        <v>87927000</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>7800000</v>
+        <v>77507000</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>7627000</v>
+        <v>71849000</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>7634000</v>
+        <v>68038000</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>7339000</v>
+        <v>64057000</v>
       </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Depreciation And Amortization</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>69335000</v>
+        <v>87927000</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>64049000</v>
+        <v>77507000</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>60411000</v>
+        <v>71849000</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>56423000</v>
+        <v>68038000</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>50101000</v>
+        <v>64057000</v>
       </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Operating Gains Losses</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="n"/>
-      <c r="C49" s="3" t="n"/>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n"/>
+          <t>Amortization Cash Flow</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>12405000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>8172000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>7800000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>7627000</v>
+      </c>
       <c r="F49" s="3" t="n">
-        <v>-94000</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>7634000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Gain Loss On Investment Securities</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="n"/>
-      <c r="C50" s="3" t="n"/>
-      <c r="D50" s="3" t="n"/>
-      <c r="E50" s="3" t="n"/>
+          <t>Amortization Of Intangibles</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>12405000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>8172000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>7800000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>7627000</v>
+      </c>
       <c r="F50" s="3" t="n">
-        <v>-94000</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>7634000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>75522000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>69335000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>64049000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>60411000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>56423000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Operating Gains Losses</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>-36362000</v>
+      </c>
+      <c r="C52" s="3" t="n"/>
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="3" t="n">
+        <v>-94000</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gain Loss On Investment Securities</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>-36362000</v>
+      </c>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n">
+        <v>-94000</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n">
+      <c r="B54" s="3" t="n">
+        <v>45966000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>61461000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>-33988000</v>
       </c>
-      <c r="D51" s="3" t="n">
-        <v>-77645000</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>-110993000</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>-92731000</v>
-      </c>
-      <c r="G51" s="3" t="n"/>
+      <c r="E54" s="3" t="n">
+        <v>-83588000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>-105050000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6637,6 +8900,18 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FY Summary</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>'Net Debt' not found in statements — left blank</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
